--- a/Risultati/Security/Report_Fix_Snyk_SonarCloud.xlsx
+++ b/Risultati/Security/Report_Fix_Snyk_SonarCloud.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescomariatorino/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescomariatorino/Desktop/Università - 0522501879/GitProject/PlayWiseDependability/Risultati/Security/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DBD336-4D6D-5F40-A1FC-C19A0891662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA38E17-8F67-5549-AC32-65C41F5A6FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -594,6 +594,7 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="5" width="29.33203125" customWidth="1"/>
   </cols>
